--- a/data/analysis_gemini_3_6_flash_no_reid/visual_event_eval_gemini_3_6_flash_no_reid.xlsx
+++ b/data/analysis_gemini_3_6_flash_no_reid/visual_event_eval_gemini_3_6_flash_no_reid.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="50">
   <si>
     <t>event</t>
   </si>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1904,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1938,6 +1938,23 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>24</v>
       </c>
     </row>
